--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_06_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_06_19_Cau.xlsx
@@ -659,7 +659,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
@@ -673,7 +677,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đổi 0,1% thành tỷ lệ rồi nhân tổng phút trong window.</t>
+          <t>Tổng số phút trong cửa sổ 30 ngày: 30 ngày * 24 giờ/ngày * 60 phút/giờ = 43.200 phút. Thời gian downtime cho phép với SLO 99,9%: 43.200 * (100% - 99,9%) = 43.200 * 0,001 = 43,2 phút.</t>
         </is>
       </c>
     </row>
@@ -803,7 +807,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Burn-rate denominator, Short window.</t>
+          <t>Quy tắc cảnh báo đa cửa sổ (multi-window multi-burn-rate) yêu cầu cả cửa sổ ngắn (5m) và cửa sổ dài (1h) đều phải vượt ngưỡng; hiện tại cửa sổ dài mới đạt 8x (&lt; 14,4x) nên không được phát trang khẩn cấp để tránh báo động giả.</t>
         </is>
       </c>
     </row>
@@ -985,7 +989,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -999,7 +1007,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Loại record duplicate trước khi sum.</t>
+          <t>Sau khi deduplicate record trùng call_id với call 0,003 USD, chi phí task chỉ tính các unique calls: 0,002 + 0,005 + 0,003 = 0,01 USD.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1137,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User, Feature.</t>
+          <t>Để phân bổ chi phí và trả lời câu hỏi của CFO về mức tiêu hao ngân sách theo từng khách hàng, bản ghi telemetry bắt buộc phải gắn thẻ định danh khách hàng (`tenant_id`).</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1225,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách population cố định trước release khỏi traffic thật sau release.</t>
+          <t>Phân biệt rạch ròi giữa offline eval và online eval: (a) Fixed benchmark trước release -&gt; offline eval; (b) Sample traffic thật sau release -&gt; online eval; (c) CI regression gate -&gt; offline eval; (d) Production drift/cohort monitoring -&gt; online eval.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_06_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_06_19_Cau.xlsx
@@ -708,10 +708,29 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Allowed bad fraction, Window duration.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Allowed bad fraction, Window duration.</t>
+- 1.0đ: Tính đúng tổng số request lỗi tối đa được phép: $200.000 \times 0.5\% = 1.000$ requests.
+- 1.0đ: Tính đúng số lượng request lỗi còn lại: $1.000 - 700 = 300$ requests.
+- 1.0đ: Tính đúng tỷ lệ phần trăm ngân sách lỗi còn lại: $30.0\%$ (đã tiêu thụ 70%).
+- 1.0đ: Đưa ra quyết định vận hành chính xác (hạn chế deploy rủi ro cao, chuẩn bị kích hoạt feature freeze nếu chạm trần).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Ngân sách Lỗi còn lại (Error Budget Calculation):
+- Tổng số yêu cầu hợp lệ được ghi nhận trong kỳ: $N = 200.000$ requests.
+- Mục tiêu cam kết SLO khả dụng: $\text{SLO} = 99.5\% = 0.995$.
+- Tỷ lệ lỗi tối đa được phép (Unreliability target): $1 - \text{SLO} = 1 - 0.995 = 0.005$ ($0.5\%$).
+- **Tổng ngân sách lỗi được phép (Total Allowed Error Budget)**:
+  $$\text{Total Allowed Bad Requests} = N \times (1 - \text{SLO}) = 200.000 \times 0.005 = \mathbf{1.000 \text{ requests}}$$
+- Số lượng yêu cầu lỗi thực tế đã xảy ra: $\text{Actual Bad Requests} = 700$ requests.
+- **Ngân sách lỗi còn lại (Remaining Error Budget)**:
+  $$\text{Remaining Bad Requests} = 1.000 - 700 = \mathbf{300 \text{ requests}}$$
+- **Tỷ lệ phần trăm ngân sách lỗi còn lại**:
+  $$\text{Percentage Remaining} = \frac{300}{1.000} \times 100\% = \mathbf{30.0\%}$$
+2. Diễn giải Vận hành &amp; Quyết định Kỹ thuật (Operational Interpretation):
+- Hệ thống đã tiêu thụ tới **70% ngân sách lỗi** ($700 / 1.000$), chỉ còn lại vỏn vẹn **30% dung sai** cho toàn bộ khoảng thời gian còn lại của chu kỳ SLO.
+- **Hành động quản trị rủi ro**: Nhóm kỹ thuật cần bước vào trạng thái cảnh giác cao (Heightened Risk State). Tạm hoãn các đợt phát hành tính năng lớn có độ rủi ro cao (risky feature releases); tăng cường kiểm thử canary trên các bản vá nhỏ; nếu số lỗi tiếp tục tăng thêm 300 requests nữa (tiêu cạn 100% budget), kích hoạt quy tắc Feature Freeze tuyệt đối theo hợp đồng SLO.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Error Budget là công cụ trung hòa mâu thuẫn giữa tính năng mới (Product) và sự ổn định (SRE). Nó biến khái niệm độ tin cậy từ tranh luận cảm tính thành một con số tài nguyên cụ thể có thể tiêu xài. Khi đã đốt hết 70% ngân sách và chỉ còn lại 30%, việc tiếp tục đẩy các thay đổi mạo hiểm là hành vi vi phạm kỷ luật vận hành SRE.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Embracing Risk &amp; The Site Reliability Workbook: Chapter 2 - Implementing SLOs</t>
         </is>
       </c>
     </row>
@@ -838,10 +857,27 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Burn-rate denominator, Short window.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Burn-rate denominator, Short window.</t>
+- 1.0đ: Đánh giá đúng cả hai điều kiện: cửa sổ 30m đạt 7x (&gt;=6x) và cửa sổ 6h đạt 6.5x (&gt;=6x).
+- 1.0đ: Kết luận chuẩn xác kết quả kết hợp: Cảnh báo Warning được kích hoạt phát lệnh chính thức (Alert Fires).
+- 1.0đ: Phân tích sâu nhược điểm nếu chỉ dùng cửa sổ ngắn (bị nhiễu transient spike, không đo được tổng tổn thất).
+- 1.0đ: Phân tích sâu nhược điểm nếu chỉ dùng cửa sổ dài (chậm phát hiện, chậm reset sau khi đã fix) và giá trị của việc kết hợp cả hai.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Kết quả Kết hợp (Joint Multiwindow Evaluation):
+- Chính sách Warning Alert 6x yêu cầu thỏa mãn đồng thời cả hai cửa sổ trượt (Logical AND):
+  + Điều kiện Cửa sổ Ngắn (30m): Tốc độ đốt $\ge 6\times$.
+  + Điều kiện Cửa sổ Dài (6h): Tốc độ đốt $\ge 6\times$.
+- Dữ liệu quan sát thực tế:
+  + Burn rate quan sát ở cửa sổ 30m là $7\times \ge 6\times$ -&gt; **THỎA MÃN (Condition 1: TRUE)**.
+  + Burn rate quan sát ở cửa sổ 6h là $6.5\times \ge 6\times$ -&gt; **THỎA MÃN (Condition 2: TRUE)**.
+- **Kết quả kết hợp (Joint Result)**: Cả hai điều kiện đều được thỏa mãn đồng thời ($7\times \ge 6\times$ VÀ $6.5\times \ge 6\times$) -&gt; **CẢNH BÁO WARNING CHÍNH THỨC ĐƯỢC PHÁT TÍN HIỆU (ALERT FIRES)**.
+2. Lý do Kỹ thuật Vì sao Bắt buộc phải dùng Hai Cửa sổ (Multiwindow Rationale):
+- **Nhược điểm chết người nếu chỉ dùng một cửa sổ ngắn (30m)**: Cửa sổ ngắn phản ứng rất nhạy, nhưng dễ bị kích hoạt bởi các xung lỗi thoáng qua (transient spikes) kéo dài vài phút rồi tự hết, gây cảnh báo giả (false alarms). Ngoài ra, khi sự cố thực sự đã được khắc phục, cửa sổ ngắn sẽ hạ nhiệt ngay lập tức, nhưng không phản ánh được tổng lượng ngân sách lỗi đã bị bốc hơi trước đó.
+- **Nhược điểm chết người nếu chỉ dùng một cửa sổ dài (6h)**: Cửa sổ dài phát hiện tốt các sự cố ngấm ngầm âm ỉ (slow burns), nhưng phản ứng quá chậm chạp khi có sự cố lớn đột ngột (high MTTD). Nguy hiểm hơn, sau khi kỹ sư đã fix xong lỗi 100%, cửa sổ 6h vẫn tiếp tục lưu giữ dữ liệu lỗi cũ trong suốt 6 tiếng tiếp theo, khiến cảnh báo bị kẹt bật liên tục (alert flapping / reset delay) dù hệ thống đã hoàn toàn bình phục.
+- **Sự kết hợp hoàn hảo**: Cửa sổ 30m bảo đảm sự cố vẫn đang thực sự tiếp diễn tại thời điểm hiện tại (active ongoing issue), trong khi cửa sổ 6h bảo đảm sự cố có quy mô tác động đủ lớn chứ không phải nhiễu mạng nhất thời.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thuật toán Multiwindow Multi-burn-rate Alerting là tiêu chuẩn vàng được Google SRE đúc kết để giải quyết triệt để bài toán đánh đổi giữa độ nhạy (sensitivity) và độ đặc hiệu (specificity). Một cảnh báo chỉ kích hoạt khi cả cửa sổ ngắn và cửa sổ dài cùng vượt ngưỡng; và cảnh báo sẽ tự động tắt ngay khi cửa sổ ngắn hạ nhiệt (ngay sau khi fix), triệt tiêu hoàn toàn hiện tượng cảnh báo giả kéo dài sau khi đã khắc phục.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook: Alerting on SLOs - Multiwindow, Multi-Burn-Rate Alerts (https://sre.google/workbook/alerting-on-slos/)</t>
         </is>
       </c>
     </row>
@@ -968,10 +1004,31 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Severity, Impact.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Severity, Impact.</t>
+- 1.0đ: Xác định chính xác cấp độ sự cố là SEV-1 / P1 và lập luận chặt chẽ dựa trên 40% enterprise traffic và no workaround.
+- 1.0đ: Thiết kế quy trình leo thang cấp 2 khi Primary không ACK sau 10 phút (chuyển sang Secondary và Team Lead).
+- 1.0đ: Thiết kế bước leo thang cấp 3 tới Incident Commander / Head of Engineering nếu tiếp tục trễ hạn.
+- 1.0đ: Mô tả quy trình thành lập War Room, phân vai Incident Commander và giao tiếp khách hàng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cấp độ Nghiêm trọng (Severity) và Quy trình Leo thang (Escalation Sequence):
+1. **Xác định Cấp độ Nghiêm trọng: SEV-1 (Major Incident / P1)**:
+- **Căn cứ xác định**:
+  + Phạm vi ảnh hưởng khổng lồ: 40% lưu lượng của phân khúc khách hàng doanh nghiệp trả phí cao nhất (Enterprise Traffic) bị gián đoạn.
+  + Hoàn toàn không có giải pháp thay thế tạm thời (No workaround available).
+  + Nguy cơ vi phạm trực tiếp thỏa thuận cam kết SLA dịch vụ và bồi thường tài chính nghiêm trọng.
+2. **Quy trình Leo thang Tự động (Automated Escalation Sequence)**:
+- **Mốc T+0m**: Hệ thống cảnh báo tự động gửi thông báo khẩn (Page) tới **Kỹ sư Trực chính (Primary On-call)** qua PagerDuty.
+- **Mốc T+10m (Primary không ACK)**:
+  + Do hết thời hạn 10 phút mà Primary không phản hồi: PagerDuty tự động leo thang (Escalate level 2) gọi điện thoại đánh thức **Kỹ sư Trực phụ (Secondary On-call)**.
+  + Đồng thời gửi tin nhắn SMS khẩn cấp tới **Engineering Team Lead** phụ trách service.
+- **Mốc T+15m (Nếu vẫn chưa có người ACK và bắt tay xử lý)**:
+  + Tự động leo thang cấp 3 (Escalate level 3): Kích hoạt quy trình Chỉ huy Sự cố Khẩn cấp (Incident Commander on-call) và thông báo tới **Head of Engineering / VP of Infrastructure**.
+3. **Thành lập Đội Ứng phó Sự cố (War Room Activation)**:
+- Ngay khi người tiếp nhận ACK, tự động mở kênh Slack khẩn cấp `#incident-sev1-enterprise-chat` và phòng họp video Google Meet / Zoom để các bên tập hợp trong 2 phút.
+- Giao quyền Incident Commander (IC) để điều phối: 1 người phụ trách điều tra kỹ thuật, 1 người phụ trách liên lạc cập nhật Status Page cho khách hàng Enterprise.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản lý Sự cố Khẩn cấp SRE: Khi 40% khách hàng doanh nghiệp bị ảnh hưởng và không có workaround, đây là tình trạng khẩn cấp cấp độ 1 (SEV-1). Quy trình on-call không được phép phụ thuộc vào sự có mặt của một cá nhân đơn lẻ. Nếu Primary không ACK trong 10 phút, chuỗi leo thang tự động (escalation policy) phải lập tức chuyển sang Secondary và cấp quản lý, đồng thời thiết lập phòng chỉ huy chiến tranh (War Room) để bảo vệ tối đa tính liên tục kinh doanh của tổ chức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+PagerDuty Incident Response Documentation: Incident Severity Levels &amp; Google SRE Book: Managing Incidents</t>
         </is>
       </c>
     </row>
@@ -1038,10 +1095,27 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Call-level usage, Multi-call task.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Call-level usage, Multi-call task.</t>
+- 1.0đ: Thiết kế cơ chế liên kết suy diễn cho các cuộc gọi mồ côi (orphan calls) bằng session_id và time-window.
+- 1.0đ: Thiết lập ngăn chi phí chưa phân bổ (Unallocated Cost Bucket) bảo đảm không làm thất thoát chi phí trên hóa đơn tổng.
+- 1.0đ: Thực thi nguyên tắc snapshot bảng giá lịch sử tại đúng thời điểm thực thi (Historical Point-in-Time Pricing).
+- 1.0đ: Xây dựng quy trình đối soát tự động cuối ngày bảo đảm cân bằng tài chính với nhà cung cấp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Cuộn chi phí Tác vụ (Agent Task Cost Rollup) và Đối soát Dữ liệu Dị biệt (Reconciliation Pipeline):
+1. **Xử lý các lời gọi LLM thiếu `task_id` (Orphan LLM Calls)**:
+- **Cơ chế Suy diễn Ngữ cảnh Thời gian và Phiên (Contextual Heuristic Matching)**:
+  Sử dụng thuật toán so khớp dựa trên các thuộc tính liên kết còn lại: `session_id`, `user_id`, và cửa sổ thời gian phát sinh lời gọi (`timestamp`). Nếu một orphan call nằm trọn vẹn trong khoảng thời gian bắt đầu và kết thúc của Task A trên cùng một session, gán có điều kiện `task_id = Task A` kèm cờ `reconciliation_method: inferred_by_session`.
+- **Ngăn lưu trữ không phân bổ (Unallocated Cost Bucket)**:
+  Nếu sau khi quét đan xen mà vẫn không thể liên kết chắc chắn với tác vụ nào, lời gọi này bắt buộc phải được chuyển vào **Khoản mục Chi phí Chưa phân bổ (`Unallocated / System Overhead Cost`)**. Tuyệt đối không xóa bỏ hoặc bỏ qua vì sẽ làm sai lệch hóa đơn tài chính tổng thể.
+2. **Xử lý Metadata Giá Token Khác nhau giữa các Ngày (Point-in-Time Cost Snapshot)**:
+- **Nguyên tắc Giá tại Thời điểm Thực thi (Historical Point-in-Time Pricing)**:
+  Giá token của một lời gọi model phải được tính toán dựa trên **Bảng giá có hiệu lực tại đúng timestamp thực thi lời gọi đó**, không bao giờ dùng bảng giá của ngày hôm nay để tính lại cho quá khứ.
+- **Cấu trúc Event Bền vững**: Ngay tại thời điểm hoàn thành lời gọi LLM, ứng dụng ghi nhận cố định các trường: `input_tokens`, `output_tokens`, `unit_rate_prompt_usd`, `unit_rate_completion_usd`, và trường tính sẵn `calculated_cost_usd`.
+3. **Quy trình Đối soát Định kỳ (Daily Reconciliation Job)**:
+- Chạy cron job cuối ngày: Tổng chi phí cuộn theo Task + Chi phí Unallocated phải khớp 100% (chênh lệch &lt; 0.001%) với hóa đơn tổng từ API provider (OpenAI/Anthropic invoice đối soát).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Tài chính AI (AI FinOps Reconciliation): Trong các hệ thống Agent phức tạp, các lời gọi model có thể bị mất correlation ID do crash hoặc async spawn, đồng thời nhà cung cấp model liên tục hạ giá theo thời gian. Nếu không có cơ chế snapshot giá tại thời điểm thực thi và không có ngăn chi phí chưa phân bổ (unallocated bucket), doanh nghiệp sẽ không thể giải trình được sự chênh lệch hàng nghìn USD giữa tổng chi phí các tác vụ và hóa đơn thực tế từ nhà cung cấp đám mây.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: FinOps for AI/ML (https://www.finops.org) &amp; OpenTelemetry Cost Metrics Conventions</t>
         </is>
       </c>
     </row>
@@ -1168,10 +1242,30 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra User, Feature.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra User, Feature.</t>
+- 1.0đ: Thiết kế đầy đủ các kích thước phân bổ chi phí chuẩn hóa (tenant, plan, feature, task_outcome, cost).
+- 1.0đ: Xây dựng báo cáo Product bóc tách chuẩn xác các tính năng có chi phí cao nhưng hoàn thành thấp (wasted cost).
+- 1.0đ: Xây dựng báo cáo Finance tính toán biên lợi nhuận (Gross Margin) bóc tách rõ ràng theo từng gói dịch vụ (Free/Pro/Enterprise).
+- 1.0đ: Đưa ra kiến nghị hành động cụ thể cho cả hai bên liên quan dựa trên số liệu báo cáo.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Phân bổ Chi phí AI (AI Cost Attribution Matrix) và Báo cáo Đa chiều:
+1. **Thiết kế Kích thước Phân bổ (Attribution Dimensions)**:
+Mỗi event tính toán phát sinh từ AI được gắn thẻ đa chiều: `tenant_id`, `subscription_plan` (Free, Pro, Enterprise), `feature_name` (Chat, Summarize, Code Gen), `task_outcome` (Success, Abandoned, Failed), và `token_cost_usd`.
+2. **Báo cáo phục vụ Nhóm Sản phẩm (Product Grouped Report: Chi phí cao vs Hoàn thành thấp)**:
+- **Chỉ số trọng tâm**: `Total Feature Spend`, `Task Completion Rate (%)`, và `Wasted Cost on Incomplete Tasks`.
+- **Mẫu báo cáo bảng phân tích**:
+  + Feature A (Tự động tra cứu hợp đồng): Chi phí: $4.500/tháng, Tỷ lệ hoàn thành: 42% -&gt; **CẢNH BÁO RỦI RO LÃNG PHÍ**: Tiêu tốn hơn $2.600 cho các phiên làm việc người dùng bỏ dở giữa chừng do agent bị kẹt loop.
+  + Feature B (Tóm tắt nhanh): Chi phí: $800/tháng, Tỷ lệ hoàn thành: 94% -&gt; Tính năng hiệu quả cao.
+- **Hành động Product**: Cần redesign lại UX và giảm bớt số bước suy luận của Feature A để tránh lãng phí tiền của công ty.
+3. **Báo cáo phục vụ Nhóm Tài chính (Finance Grouped Report: Biên lợi nhuận theo Gói dịch vụ)**:
+- **Chỉ số trọng tâm**: `Subscription Revenue`, `AI Model Cost`, `Gross Margin (%)` tính theo từng gói (`subscription_plan`).
+- **Mẫu báo cáo bảng phân tích**:
+  + Gói Free: Doanh thu: $0, Chi phí AI: $1.200/tháng -&gt; Chi phí duy trì người dùng miễn phí (Cần đặt hạn ngạch quota chặt chẽ hơn).
+  + Gói Pro ($30/tháng/user): Doanh thu: $30.000, Chi phí AI: $9.000 -&gt; Gross Margin = **70%** (Đạt chỉ tiêu tài chính SaaS).
+  + Gói Enterprise: Doanh thu: $100.000, Chi phí AI: $45.000 -&gt; Gross Margin = **55%** (Cần xem xét phụ phí nếu một số tenant dùng quá tải token).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân bổ Chi phí Đơn vị (Unit Economics &amp; Cost Attribution in AI): Một khoản chi phí AI $50.000/tháng là vô nghĩa nếu không thể bóc tách thành giá trị kinh doanh. Nhóm Sản phẩm cần nhìn thấy tính năng nào 'đốt tiền' mà không mang lại kết quả (High cost - Low completion) để tối ưu luồng nghiệp vụ; trong khi nhóm Tài chính cần nhìn thấy biên lợi nhuận ròng (Gross Margin) trên từng gói thuê bao để đảm bảo mô hình kinh doanh có lãi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: Cloud Cost Allocation (https://www.finops.org/framework/capabilities/cost-allocation/) &amp; Andreessen Horowitz: The New Business of AI</t>
         </is>
       </c>
     </row>
@@ -1256,10 +1350,26 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Fixed test set, Production traffic.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Fixed test set, Production traffic.</t>
+- 1.0đ: Đưa ra lựa chọn kết hợp cả hai (Both) và giải thích rõ vai trò chiến lược của từng phương pháp.
+- 1.0đ: Trình bày vai trò kiểm định hồi quy nền tảng của Offline Benchmark từ tuần trước.
+- 1.0đ: Trình bày vai trò phát hiện sự cố thời gian thực qua tín hiệu gián tiếp của Online Evaluation.
+- 1.0đ: Phân tích sâu sắc giới hạn cốt tử của mỗi phương pháp (tính tĩnh của benchmark vs sự thiếu vắng ground truth của online).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lựa chọn Chiến lược Đánh giá (Online / Offline / Both) và Phân định Giới hạn:
+1. **Lựa chọn Chiến lược Tối ưu: KẾT HỢP CẢ HAI (BOTH) theo vai trò bổ trợ**:
+- **Vai trò của Offline Evaluation (Dùng Benchmark tuần trước)**:
+  + Ngay khi nhận phản ánh sự cố chất lượng: Lấy tập Golden Benchmark curated từ tuần trước đem chạy kiểm thử hồi quy (regression test) tức thì với phiên bản prompt/model hiện tại.
+  + Mục đích: Xác định xem năng lực cốt lõi của model có bị suy thoái so với baseline tuần trước hay không. Nếu điểm số trên offline benchmark giảm mạnh, khẳng định model đã bị trôi dạt (model drift/regression).
+- **Vai trò của Online Evaluation (Giám sát Real-time Traffic)**:
+  + Thu thập ngay lập tức các tín hiệu không cần ground truth tức thời: Tỷ lệ người dùng phàn nàn (negative feedback/thumbs-down), tỷ lệ bấm regenerate, độ dài câu trả lời bất thường, và chấm điểm không tham chiếu (reference-free metrics như LLM-as-a-judge checking for toxicity/relevance).
+  + Mục đích: Khoanh vùng chính xác các ca lỗi thực tế đang diễn ra trên production để trích xuất dữ liệu mới.
+2. **Giới hạn Cốt tử của Từng Phương pháp (Boundaries &amp; Limitations)**:
+- **Giới hạn của Offline Benchmark**: Tập dữ liệu của tuần trước là tĩnh (static). Nó không bao quát được các chủ đề mới phát sinh trong tuần này (out-of-distribution queries / new corpus drift). Hệ thống có thể đạt 100% trên benchmark cũ nhưng vẫn thất bại hoàn toàn trên traffic mới của người dùng.
+- **Giới hạn của Online Evaluation không có Ground Truth**: Các phương pháp đánh giá online không tham chiếu (reference-free LLM judge) có độ tự tin thấp hơn, dễ bị sai lệch chủ quan (judge bias, hallucinations of the judge), và không thể khẳng định 100% tính đúng sai của các câu trả lời chuyên môn sâu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự cố chất lượng trong AI đòi hỏi sự phối hợp nhịp nhàng giữa Online và Offline Evaluation. Offline Benchmark là chốt chặn kiểm soát hồi quy có độ tin cậy tuyệt đối nhưng mang tính quá khứ và tĩnh tại. Online Monitoring bắt kịp nhịp đập thực tế của người dùng nhưng thiếu nhãn chân lý (ground truth) tức thời. Kết hợp cả hai: dùng Offline để kiểm tra sức khỏe nền tảng của mô hình, và dùng Online để phát hiện các lỗ hổng tri thức mới phát sinh ngoài thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain &amp; LangSmith Documentation: Offline vs Online Evaluation Frameworks &amp; Shreya Shankar: Operationalizing ML Evaluation</t>
         </is>
       </c>
     </row>
@@ -1338,10 +1448,27 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Explicit rating, Implicit behavior.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Explicit rating, Implicit behavior.</t>
+- 1.0đ: Phân tích và lý giải thấu đáo nghịch lý phản hồi (copy cao nhưng thực chất là copy để tự sửa do không hài lòng).
+- 1.0đ: Thiết kế các chỉ số tinh chỉnh phân tích hành vi (copy_to_resolution, dwell time sau copy).
+- 1.0đ: Thiết lập quy trình lấy mẫu phân đoạn có chủ đích (targeted cohort sampling 50 ca lỗi).
+- 1.0đ: Đưa ra lộ trình kiểm chứng định tính qua rà soát nội dung và khảo sát vi mô xác nhận nguyên nhân.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Metric và Lộ trình Kiểm chứng Tín hiệu Phản hồi Con người (Human Feedback Signal Interpretation):
+1. **Phân tích Nghịch lý Dữ liệu (Satisfaction Paradox)**:
+- Hiện tượng: `Copy-rate cao` (người dùng copy text nhiều) thường được coi là tín hiệu tích cực (positive signal). Tuy nhiên, đồng thời `Abandonment-rate cao` (người dùng rời bỏ phiên chat) và `Rating thấp ở nhóm nhỏ`.
+- **Chẩn đoán nghịch lý**: Người dùng copy câu trả lời KHÔNG PHẢI VÌ HÀI LÒNG, mà vì họ copy nội dung ra ngoài để tự sửa lỗi thủ công bằng tay (Manual Editing / Paraphrase Failure), sau đó thất vọng bỏ cuộc không tiếp tục tương tác với chatbot nữa.
+2. **Thiết kế Chỉ số Định lượng Bóc tách (Refined Feedback Metrics)**:
+- `copy_to_resolution_ratio`: Tỷ lệ các phiên có hành vi copy dẫn đến kết thúc tác vụ thành công thay vì thoát đột ngột.
+- `dwell_time_after_copy`: Thời gian người dùng ở lại trang sau khi copy. Nếu &lt; 5 giây rồi đóng tab, đó là hành vi cứu vãn dữ liệu rồi rời đi (Frustrated Abandonment).
+- `re_prompt_after_copy_rate`: Tỷ lệ người dùng paste lại chính đoạn text vừa copy để yêu cầu 'sửa lại cho tôi'.
+3. **Lộ trình Kiểm chứng Xác nhận (Confirmation Path)**:
+- **Bước 1 - Lấy mẫu phân đoạn (Cohort Sampling)**: Lọc chính xác 50 phiên làm việc thuộc nhóm người dùng có hành vi (Copy + Rating Thấp + Thoát phiên).
+- **Bước 2 - Đánh giá Chuyên gia Ngữ nghĩa (Qualitative Inspection)**: Đội ngũ Product/SRE đọc trực tiếp prompt và câu trả lời của 50 ca này. Kiểm tra xem câu trả lời có đúng format nhưng sai số liệu, hoặc giọng điệu quá cứng nhắc khiến người dùng phải copy ra chỉnh sửa hay không.
+- **Bước 3 - Khảo sát vi mô tại chỗ (Micro-survey)**: Khi người dùng bấm copy rồi có cử chỉ rê chuột định đóng tab, hiển thị popup 1 câu hỏi nhẹ nhàng: 'Nội dung này có cần bạn phải chỉnh sửa lại không?' để thu thập bằng chứng xác nhận trực tiếp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cạm bẫy lớn nhất trong việc phân tích phản hồi ngầm định của người dùng (Implicit User Feedback) là ngộ nhận hành vi. Một hành vi tưởng như tích cực (Copy văn bản) có thể che giấu sự ức chế tột độ của khách hàng khi câu trả lời bị sai một chi tiết nhỏ buộc họ phải tự sửa bằng tay. Việc kết hợp nhiều tín hiệu tương phản (Copy kết hợp Abandonment và Rating thấp) và tiến hành điều tra mẫu định tính giúp bóc trần sự thật đằng sau những con số thống kê bề mặt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Eugene Yan: Patterns for Building LLM-based Systems &amp; Google SRE Workbook: User-Centric Metrics</t>
         </is>
       </c>
     </row>
